--- a/artfynd/A 33816-2023 artfynd.xlsx
+++ b/artfynd/A 33816-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33816-2023 artfynd.xlsx
+++ b/artfynd/A 33816-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>111351788</v>
       </c>
       <c r="B2" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604748.7335267933</v>
+        <v>604749</v>
       </c>
       <c r="R2" t="n">
-        <v>6422599.523754241</v>
+        <v>6422600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,12 +787,7 @@
         <v>111351811</v>
       </c>
       <c r="B3" t="n">
-        <v>89425</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604741.2615550801</v>
+        <v>604741</v>
       </c>
       <c r="R3" t="n">
-        <v>6422539.299224842</v>
+        <v>6422539</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
